--- a/output/Tables/Modal shift/modalshift_km_CO2_emit.xlsx
+++ b/output/Tables/Modal shift/modalshift_km_CO2_emit.xlsx
@@ -8,14 +8,27 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ines/Documents/PhD/PROJETS/MARCHE/HIA_walking_steps/output/Tables/Modal shift/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE57D131-8C7B-514A-86F6-CFFA87831F5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F80FB96B-80FF-EE4A-9456-EB74D6498C5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="500" windowWidth="16100" windowHeight="9660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -52,34 +65,34 @@
     <t>324.299 (297.155 - 354.161)</t>
   </si>
   <si>
-    <t>Mean CO2 emissions prevented (kt CO2)</t>
-  </si>
-  <si>
-    <t>Mean CO2 emissions prevented (kt CO2, Rubin)</t>
-  </si>
-  <si>
-    <t>Total CO2 emissions diminution (kt CO2)</t>
+    <t>Mean CO2 emissions prevented (gCO2)</t>
+  </si>
+  <si>
+    <t>Mean CO2 emissions prevented (gCO2, Rubin)</t>
+  </si>
+  <si>
+    <t>Total reduced CO2 emissions emitted (kt CO2)</t>
   </si>
   <si>
     <t>4836.208 (4124.004 - 5654.685)</t>
   </si>
   <si>
-    <t>Total CO2 emissions diminution (kt CO2, Rubin)</t>
+    <t>Total reduced CO2 emissions emitted (kt CO2, Rubin)</t>
   </si>
   <si>
     <t>4836.116 (4126.361 - 5653.227)</t>
   </si>
   <si>
-    <t>Mean CO2 emissions reduction (kt CO2)</t>
-  </si>
-  <si>
-    <t>0.2 (0.176 - 0.225)</t>
-  </si>
-  <si>
-    <t>Mean CO2 emissions reduction (kt CO2, Rubin)</t>
-  </si>
-  <si>
-    <t>0.2 (0.177 - 0.225)</t>
+    <t>Mean CO2 emissions reduction (%)</t>
+  </si>
+  <si>
+    <t>-20.007 (-22.516 - -17.667)</t>
+  </si>
+  <si>
+    <t>Mean CO2 emissions reduction (%, Rubin)</t>
+  </si>
+  <si>
+    <t>-19.995 (-22.513 - -17.658)</t>
   </si>
 </sst>
 </file>
@@ -435,7 +448,7 @@
   <dimension ref="A1:B11"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="37.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="41.5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>

--- a/output/Tables/Modal shift/modalshift_km_CO2_emit.xlsx
+++ b/output/Tables/Modal shift/modalshift_km_CO2_emit.xlsx
@@ -1,105 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10119"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ines/Documents/PhD/PROJETS/MARCHE/HIA_walking_steps/output/Tables/Modal shift/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F80FB96B-80FF-EE4A-9456-EB74D6498C5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="500" windowWidth="16100" windowHeight="9660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="20">
-  <si>
-    <t>measure</t>
-  </si>
-  <si>
-    <t>value</t>
-  </si>
-  <si>
-    <t>Total distance shifted (Mkm)</t>
-  </si>
-  <si>
-    <t>2382.313 (2216.222 - 2563.059)</t>
-  </si>
-  <si>
-    <t>Total distance shifted (Mkm, Rubin)</t>
-  </si>
-  <si>
-    <t>2383.908 (2210.837 - 2556.978)</t>
-  </si>
-  <si>
-    <t>CO2 emissions prevented (kt CO2)</t>
-  </si>
-  <si>
-    <t>324.285 (297.204 - 354.194)</t>
-  </si>
-  <si>
-    <t>CO2 emissions prevented (kt CO2, Rubin)</t>
-  </si>
-  <si>
-    <t>324.299 (297.155 - 354.161)</t>
-  </si>
-  <si>
-    <t>Mean CO2 emissions prevented (gCO2)</t>
-  </si>
-  <si>
-    <t>Mean CO2 emissions prevented (gCO2, Rubin)</t>
-  </si>
-  <si>
-    <t>Total reduced CO2 emissions emitted (kt CO2)</t>
-  </si>
-  <si>
-    <t>4836.208 (4124.004 - 5654.685)</t>
-  </si>
-  <si>
-    <t>Total reduced CO2 emissions emitted (kt CO2, Rubin)</t>
-  </si>
-  <si>
-    <t>4836.116 (4126.361 - 5653.227)</t>
-  </si>
-  <si>
-    <t>Mean CO2 emissions reduction (%)</t>
-  </si>
-  <si>
-    <t>-20.007 (-22.516 - -17.667)</t>
-  </si>
-  <si>
-    <t>Mean CO2 emissions reduction (%, Rubin)</t>
-  </si>
-  <si>
-    <t>-19.995 (-22.513 - -17.658)</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -147,21 +63,13 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -199,7 +107,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -233,7 +141,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -268,10 +175,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -444,100 +350,188 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B11"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="41.5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="26.6640625" bestFit="1" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:B15"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>10</v>
-      </c>
-      <c r="B6" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
-        <v>11</v>
-      </c>
-      <c r="B7" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
-        <v>12</v>
-      </c>
-      <c r="B8" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
-        <v>14</v>
-      </c>
-      <c r="B9" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
-        <v>16</v>
-      </c>
-      <c r="B10" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A11" t="s">
-        <v>18</v>
-      </c>
-      <c r="B11" t="s">
-        <v>19</v>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>measure</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Total distance shifted (Mkm)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2382.313 (2216.222 - 2563.059)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Total distance shifted (Mkm, Rubin)</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2383.908 (2210.837 - 2556.978)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>CO2 emissions emitted in 2019 by shifted drivers (kt CO2)</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>5178.702 (4449.684 - 6012.439)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>CO2 emissions emitted in 2019 by shifted drivers (kt CO2, Rubin)</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>5178.702 (4449.684 - 6012.439)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Mean CO2 emissions emitted in 2019 by shifted drivers (gCO2)</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>176951.765 (156018.304 - 200132.458)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Mean CO2 emissions emitted in 2019 by shifted drivers (gCO2, Rubin)</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>176951.765 (156018.304 - 200132.458)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>CO2 emissions prevented (kt CO2)</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>324.348 (297.254 - 354.229)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>CO2 emissions prevented (kt CO2, Rubin)</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>324.348 (297.254 - 354.229)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Mean CO2 emissions prevented (gCO2)</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>11115.103 (10330.666 - 11904.352)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Mean CO2 emissions prevented (gCO2, Rubin)</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>11115.103 (10330.666 - 11904.352)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Total reduced CO2 emissions emitted for short car trips (kt CO2)</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>4837.098 (4120.944 - 5657.435)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Total reduced CO2 emissions emitted for short car trips (kt CO2, Rubin)</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>4837.098 (4120.944 - 5657.435)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Mean CO2 emissions reduction (%)</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>-19.998 (-22.504 - -17.649)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Mean CO2 emissions reduction (%, Rubin)</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>-19.998 (-22.504 - -17.649)</t>
+        </is>
       </c>
     </row>
   </sheetData>
